--- a/output/pdf_financials_xlsx/CRPC.xlsx
+++ b/output/pdf_financials_xlsx/CRPC.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.922171</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.922171</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.922171</v>
       </c>
     </row>
     <row r="93">
@@ -2990,7 +2990,11 @@
           <t>Reserve 6</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>2.922171</v>
       </c>

--- a/output/pdf_financials_xlsx/CRPC.xlsx
+++ b/output/pdf_financials_xlsx/CRPC.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.046128</v>
+        <v>3.060208</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.040211</v>
+        <v>0.534659</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.032863</v>
+        <v>0.555885</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.046128</v>
+        <v>-3.060208</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.040211</v>
+        <v>-0.534659</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.032863</v>
+        <v>-0.555885</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.101991</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.099012</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.057987</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.958217</v>
+        <v>-3.060208</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.435647</v>
+        <v>-0.534659</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.384031</v>
+        <v>-0.442018</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.958217</v>
+        <v>-3.060208</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.435647</v>
+        <v>-0.534659</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.384031</v>
+        <v>-0.442018</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.666722</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.988051</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.483684</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.666722</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.988051</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.483684</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.68091</v>
+        <v>0.014188</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.002219</v>
+        <v>0.014168</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.500872</v>
+        <v>0.017188</v>
       </c>
     </row>
     <row r="49">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-3.060208</v>
+        <v>3.060208</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.534659</v>
+        <v>0.534659</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.555885</v>
+        <v>0.555885</v>
       </c>
     </row>
     <row r="42">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRPC.xlsx
+++ b/output/pdf_financials_xlsx/CRPC.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.046128</v>
+        <v>0.468145</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.040211</v>
+        <v>0.261443</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.032863</v>
+        <v>0.268828</v>
       </c>
     </row>
     <row r="8">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.11751</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.118768</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.02393</v>
       </c>
     </row>
     <row r="65">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.14501</v>
+        <v>0.26252</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.147368</v>
+        <v>0.266136</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.04493</v>
+        <v>0.06886</v>
       </c>
     </row>
     <row r="69">
@@ -3635,7 +3635,11 @@
           <t>Consulting, management and directors fees 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.422017</v>
       </c>
